--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124663875</v>
+        <v>124667161</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>96445</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +941,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633040</v>
+        <v>632898</v>
       </c>
       <c r="R4" t="n">
-        <v>6898800</v>
+        <v>6898903</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124665963</v>
+        <v>124676227</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>79764</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,46 +1049,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633052</v>
+        <v>633194</v>
       </c>
       <c r="R5" t="n">
-        <v>6898874</v>
+        <v>6898707</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,19 +1113,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:46</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,6 +1129,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1154,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124664744</v>
+        <v>124664023</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,47 +1160,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633172</v>
+        <v>633092</v>
       </c>
       <c r="R6" t="n">
-        <v>6898735</v>
+        <v>6898802</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1238,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124664924</v>
+        <v>124664616</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>74840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,25 +1281,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633183</v>
+        <v>633153</v>
       </c>
       <c r="R7" t="n">
-        <v>6898714</v>
+        <v>6898758</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1350,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664616</v>
+        <v>124663369</v>
       </c>
       <c r="B8" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,38 +1393,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633153</v>
+        <v>632999</v>
       </c>
       <c r="R8" t="n">
-        <v>6898758</v>
+        <v>6898916</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1462,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124667161</v>
+        <v>124665555</v>
       </c>
       <c r="B9" t="n">
-        <v>96445</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,34 +1518,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>990</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632898</v>
+        <v>633142</v>
       </c>
       <c r="R9" t="n">
-        <v>6898903</v>
+        <v>6898840</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1574,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124676227</v>
+        <v>124664466</v>
       </c>
       <c r="B10" t="n">
-        <v>79764</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,44 +1635,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633194</v>
+        <v>633170</v>
       </c>
       <c r="R10" t="n">
-        <v>6898707</v>
+        <v>6898718</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,14 +1696,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1717,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1722,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124667024</v>
+        <v>124665985</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,25 +1747,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1762,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632896</v>
+        <v>633054</v>
       </c>
       <c r="R11" t="n">
-        <v>6898908</v>
+        <v>6898879</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,26 +1831,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1854,7 +1847,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664466</v>
+        <v>124664327</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1894,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633170</v>
+        <v>633161</v>
       </c>
       <c r="R12" t="n">
-        <v>6898718</v>
+        <v>6898722</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1929,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124664023</v>
+        <v>124663547</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>74840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,46 +1975,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633092</v>
+        <v>633000</v>
       </c>
       <c r="R13" t="n">
-        <v>6898802</v>
+        <v>6898916</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,7 +2044,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124663547</v>
+        <v>124665963</v>
       </c>
       <c r="B14" t="n">
-        <v>74840</v>
+        <v>4772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,37 +2092,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633000</v>
+        <v>633052</v>
       </c>
       <c r="R14" t="n">
-        <v>6898916</v>
+        <v>6898874</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,12 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,10 +2193,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124665985</v>
+        <v>124666936</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,38 +2205,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633054</v>
+        <v>632907</v>
       </c>
       <c r="R15" t="n">
-        <v>6898879</v>
+        <v>6898900</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2279,7 +2277,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2289,7 +2287,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,7 +2314,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124665555</v>
+        <v>124667201</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2351,7 +2349,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2365,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633142</v>
+        <v>632898</v>
       </c>
       <c r="R16" t="n">
-        <v>6898840</v>
+        <v>6898903</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2400,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2408,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124663369</v>
+        <v>124664880</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,47 +2447,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632999</v>
+        <v>633177</v>
       </c>
       <c r="R17" t="n">
-        <v>6898916</v>
+        <v>6898718</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2521,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2531,7 +2520,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124667201</v>
+        <v>124664924</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2570,47 +2559,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632898</v>
+        <v>633183</v>
       </c>
       <c r="R18" t="n">
-        <v>6898903</v>
+        <v>6898714</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2642,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124666936</v>
+        <v>124663875</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2712,26 +2692,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632907</v>
+        <v>633040</v>
       </c>
       <c r="R19" t="n">
-        <v>6898900</v>
+        <v>6898800</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2763,7 +2734,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2744,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2800,10 +2771,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124664880</v>
+        <v>124664744</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2812,38 +2783,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633177</v>
+        <v>633172</v>
       </c>
       <c r="R20" t="n">
-        <v>6898718</v>
+        <v>6898735</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2912,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124664327</v>
+        <v>124667024</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,34 +2908,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633161</v>
+        <v>632896</v>
       </c>
       <c r="R21" t="n">
-        <v>6898722</v>
+        <v>6898908</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2977,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,6 +2988,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667161</v>
+        <v>124664616</v>
       </c>
       <c r="B4" t="n">
-        <v>96445</v>
+        <v>74840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,38 +937,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>990</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632898</v>
+        <v>633153</v>
       </c>
       <c r="R4" t="n">
-        <v>6898903</v>
+        <v>6898758</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124676227</v>
+        <v>124664327</v>
       </c>
       <c r="B5" t="n">
-        <v>79764</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,44 +1049,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>392</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633194</v>
+        <v>633161</v>
       </c>
       <c r="R5" t="n">
-        <v>6898707</v>
+        <v>6898722</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,14 +1110,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,7 +1131,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124664023</v>
+        <v>124666936</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,35 +1161,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1197,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633092</v>
+        <v>632907</v>
       </c>
       <c r="R6" t="n">
-        <v>6898802</v>
+        <v>6898900</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124664616</v>
+        <v>124667024</v>
       </c>
       <c r="B7" t="n">
-        <v>74840</v>
+        <v>96354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,38 +1282,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633153</v>
+        <v>632896</v>
       </c>
       <c r="R7" t="n">
-        <v>6898758</v>
+        <v>6898908</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,6 +1366,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1381,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124663369</v>
+        <v>124676227</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79764</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,46 +1418,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632999</v>
+        <v>633194</v>
       </c>
       <c r="R8" t="n">
-        <v>6898916</v>
+        <v>6898707</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,19 +1478,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,6 +1494,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1502,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124665555</v>
+        <v>124667201</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1537,7 +1548,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1551,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633142</v>
+        <v>632898</v>
       </c>
       <c r="R9" t="n">
-        <v>6898840</v>
+        <v>6898903</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1735,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124665985</v>
+        <v>124663875</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,25 +1758,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633054</v>
+        <v>633040</v>
       </c>
       <c r="R11" t="n">
-        <v>6898879</v>
+        <v>6898800</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1810,7 +1821,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,7 +1831,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1858,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664327</v>
+        <v>124664744</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,38 +1870,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633161</v>
+        <v>633172</v>
       </c>
       <c r="R12" t="n">
-        <v>6898722</v>
+        <v>6898735</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1922,7 +1942,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1952,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1979,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124663547</v>
+        <v>124667161</v>
       </c>
       <c r="B13" t="n">
-        <v>74840</v>
+        <v>96445</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,25 +1991,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,13 +2019,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633000</v>
+        <v>632898</v>
       </c>
       <c r="R13" t="n">
-        <v>6898916</v>
+        <v>6898903</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2054,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,12 +2064,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2193,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124666936</v>
+        <v>124663547</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2205,50 +2220,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632907</v>
+        <v>633000</v>
       </c>
       <c r="R15" t="n">
-        <v>6898900</v>
+        <v>6898916</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2277,7 +2283,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2287,7 +2293,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,10 +2325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124667201</v>
+        <v>124664880</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,47 +2337,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632898</v>
+        <v>633177</v>
       </c>
       <c r="R16" t="n">
-        <v>6898903</v>
+        <v>6898718</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2398,7 +2400,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,7 +2410,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,10 +2437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664880</v>
+        <v>124664924</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2451,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2475,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633177</v>
+        <v>633183</v>
       </c>
       <c r="R17" t="n">
-        <v>6898718</v>
+        <v>6898714</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2547,10 +2549,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124664924</v>
+        <v>124665985</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2559,38 +2561,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633183</v>
+        <v>633054</v>
       </c>
       <c r="R18" t="n">
-        <v>6898714</v>
+        <v>6898879</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2622,7 +2624,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2634,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2661,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124663875</v>
+        <v>124664023</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2671,38 +2673,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633040</v>
+        <v>633092</v>
       </c>
       <c r="R19" t="n">
-        <v>6898800</v>
+        <v>6898802</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2771,7 +2782,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124664744</v>
+        <v>124665555</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2806,7 +2817,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2816,14 +2827,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633172</v>
+        <v>633142</v>
       </c>
       <c r="R20" t="n">
-        <v>6898735</v>
+        <v>6898840</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2855,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124667024</v>
+        <v>124663369</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2904,38 +2915,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632896</v>
+        <v>632999</v>
       </c>
       <c r="R21" t="n">
-        <v>6898908</v>
+        <v>6898916</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2967,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,26 +3008,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664616</v>
+        <v>124664466</v>
       </c>
       <c r="B4" t="n">
-        <v>74840</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633153</v>
+        <v>633170</v>
       </c>
       <c r="R4" t="n">
-        <v>6898758</v>
+        <v>6898718</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664327</v>
+        <v>124667201</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,38 +1049,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633161</v>
+        <v>632898</v>
       </c>
       <c r="R5" t="n">
-        <v>6898722</v>
+        <v>6898903</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124666936</v>
+        <v>124667024</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,47 +1170,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632907</v>
+        <v>632896</v>
       </c>
       <c r="R6" t="n">
-        <v>6898900</v>
+        <v>6898908</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,6 +1254,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124667024</v>
+        <v>124665963</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,38 +1302,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632896</v>
+        <v>633052</v>
       </c>
       <c r="R7" t="n">
-        <v>6898908</v>
+        <v>6898874</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,26 +1391,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1402,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124676227</v>
+        <v>124664880</v>
       </c>
       <c r="B8" t="n">
-        <v>79764</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,44 +1419,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633194</v>
+        <v>633177</v>
       </c>
       <c r="R8" t="n">
-        <v>6898707</v>
+        <v>6898718</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1478,14 +1480,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,7 +1501,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1513,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124667201</v>
+        <v>124664616</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,47 +1531,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632898</v>
+        <v>633153</v>
       </c>
       <c r="R9" t="n">
-        <v>6898903</v>
+        <v>6898758</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1597,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124664466</v>
+        <v>124665985</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,38 +1643,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633170</v>
+        <v>633054</v>
       </c>
       <c r="R10" t="n">
-        <v>6898718</v>
+        <v>6898879</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1709,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124663875</v>
+        <v>124663547</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,25 +1755,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,13 +1783,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633040</v>
+        <v>633000</v>
       </c>
       <c r="R11" t="n">
-        <v>6898800</v>
+        <v>6898916</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1831,7 +1828,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,10 +1860,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664744</v>
+        <v>124664023</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,47 +1872,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633172</v>
+        <v>633092</v>
       </c>
       <c r="R12" t="n">
-        <v>6898735</v>
+        <v>6898802</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1942,7 +1944,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1952,7 +1954,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124667161</v>
+        <v>124676227</v>
       </c>
       <c r="B13" t="n">
-        <v>96445</v>
+        <v>79764</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,37 +1997,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>990</v>
+        <v>392</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632898</v>
+        <v>633194</v>
       </c>
       <c r="R13" t="n">
-        <v>6898903</v>
+        <v>6898707</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,19 +2057,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:17</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,6 +2073,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2091,10 +2092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124665963</v>
+        <v>124663369</v>
       </c>
       <c r="B14" t="n">
-        <v>4772</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,31 +2104,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2136,10 +2141,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633052</v>
+        <v>632999</v>
       </c>
       <c r="R14" t="n">
-        <v>6898874</v>
+        <v>6898916</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2171,7 +2176,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124663547</v>
+        <v>124665555</v>
       </c>
       <c r="B15" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,41 +2225,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633000</v>
+        <v>633142</v>
       </c>
       <c r="R15" t="n">
-        <v>6898916</v>
+        <v>6898840</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2283,7 +2297,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2293,12 +2307,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,10 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124664880</v>
+        <v>124663875</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,38 +2346,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633177</v>
+        <v>633040</v>
       </c>
       <c r="R16" t="n">
-        <v>6898718</v>
+        <v>6898800</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2400,7 +2409,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2419,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124665985</v>
+        <v>124664327</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2561,38 +2570,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633054</v>
+        <v>633161</v>
       </c>
       <c r="R18" t="n">
-        <v>6898879</v>
+        <v>6898722</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2624,7 +2633,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2634,7 +2643,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,10 +2670,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124664023</v>
+        <v>124666936</v>
       </c>
       <c r="B19" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,35 +2682,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2710,10 +2719,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633092</v>
+        <v>632907</v>
       </c>
       <c r="R19" t="n">
-        <v>6898802</v>
+        <v>6898900</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2745,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2755,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,7 +2791,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124665555</v>
+        <v>124664744</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2817,7 +2826,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2827,14 +2836,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633142</v>
+        <v>633172</v>
       </c>
       <c r="R20" t="n">
-        <v>6898840</v>
+        <v>6898735</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2866,7 +2875,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2885,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,10 +2912,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124663369</v>
+        <v>124667161</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>96445</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2919,43 +2928,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>990</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632999</v>
+        <v>632898</v>
       </c>
       <c r="R21" t="n">
-        <v>6898916</v>
+        <v>6898903</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664466</v>
+        <v>124667161</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>96445</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,38 +937,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633170</v>
+        <v>632898</v>
       </c>
       <c r="R4" t="n">
-        <v>6898718</v>
+        <v>6898903</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1037,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124667201</v>
+        <v>124664744</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1082,14 +1082,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632898</v>
+        <v>633172</v>
       </c>
       <c r="R5" t="n">
-        <v>6898903</v>
+        <v>6898735</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124665963</v>
+        <v>124664466</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,43 +1302,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633052</v>
+        <v>633170</v>
       </c>
       <c r="R7" t="n">
-        <v>6898874</v>
+        <v>6898718</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1370,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664880</v>
+        <v>124664924</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1423,21 +1418,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1447,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633177</v>
+        <v>633183</v>
       </c>
       <c r="R8" t="n">
-        <v>6898718</v>
+        <v>6898714</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1519,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124664616</v>
+        <v>124664880</v>
       </c>
       <c r="B9" t="n">
-        <v>74840</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,25 +1526,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633153</v>
+        <v>633177</v>
       </c>
       <c r="R9" t="n">
-        <v>6898758</v>
+        <v>6898718</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1594,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124665985</v>
+        <v>124665555</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,38 +1638,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633054</v>
+        <v>633142</v>
       </c>
       <c r="R10" t="n">
-        <v>6898879</v>
+        <v>6898840</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1706,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1720,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124663547</v>
+        <v>124676227</v>
       </c>
       <c r="B11" t="n">
-        <v>74840</v>
+        <v>79764</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,38 +1759,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633000</v>
+        <v>633194</v>
       </c>
       <c r="R11" t="n">
-        <v>6898916</v>
+        <v>6898707</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,24 +1823,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,6 +1839,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1860,10 +1858,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664023</v>
+        <v>124664327</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,47 +1870,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633092</v>
+        <v>633161</v>
       </c>
       <c r="R12" t="n">
-        <v>6898802</v>
+        <v>6898722</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1944,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1954,7 +1943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124676227</v>
+        <v>124666936</v>
       </c>
       <c r="B13" t="n">
-        <v>79764</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,40 +1986,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633194</v>
+        <v>632907</v>
       </c>
       <c r="R13" t="n">
-        <v>6898707</v>
+        <v>6898900</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2057,14 +2052,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,7 +2073,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2092,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124663369</v>
+        <v>124664616</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,47 +2103,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632999</v>
+        <v>633153</v>
       </c>
       <c r="R14" t="n">
-        <v>6898916</v>
+        <v>6898758</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2176,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2186,7 +2176,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124665555</v>
+        <v>124663547</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,50 +2215,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633142</v>
+        <v>633000</v>
       </c>
       <c r="R15" t="n">
-        <v>6898840</v>
+        <v>6898916</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2297,7 +2278,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,7 +2288,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2334,10 +2320,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124663875</v>
+        <v>124665963</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>4772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,38 +2332,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633040</v>
+        <v>633052</v>
       </c>
       <c r="R16" t="n">
-        <v>6898800</v>
+        <v>6898874</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2409,7 +2400,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2419,7 +2410,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,10 +2437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664924</v>
+        <v>124664023</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2458,38 +2449,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633183</v>
+        <v>633092</v>
       </c>
       <c r="R17" t="n">
-        <v>6898714</v>
+        <v>6898802</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124664327</v>
+        <v>124665985</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2570,38 +2570,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633161</v>
+        <v>633054</v>
       </c>
       <c r="R18" t="n">
-        <v>6898722</v>
+        <v>6898879</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,7 +2670,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124666936</v>
+        <v>124663369</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632907</v>
+        <v>632999</v>
       </c>
       <c r="R19" t="n">
-        <v>6898900</v>
+        <v>6898916</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,7 +2791,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124664744</v>
+        <v>124663875</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2824,26 +2824,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633172</v>
+        <v>633040</v>
       </c>
       <c r="R20" t="n">
-        <v>6898735</v>
+        <v>6898800</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2875,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2885,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2912,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124667161</v>
+        <v>124667201</v>
       </c>
       <c r="B21" t="n">
-        <v>96445</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,24 +2919,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>990</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667161</v>
+        <v>124664924</v>
       </c>
       <c r="B4" t="n">
-        <v>96445</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,38 +937,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>990</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632898</v>
+        <v>633183</v>
       </c>
       <c r="R4" t="n">
-        <v>6898903</v>
+        <v>6898714</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1037,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664744</v>
+        <v>124665555</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1082,14 +1082,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633172</v>
+        <v>633142</v>
       </c>
       <c r="R5" t="n">
-        <v>6898735</v>
+        <v>6898840</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124667024</v>
+        <v>124667201</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,38 +1170,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632896</v>
+        <v>632898</v>
       </c>
       <c r="R6" t="n">
-        <v>6898908</v>
+        <v>6898903</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,26 +1263,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124664466</v>
+        <v>124667161</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>96445</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,38 +1291,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633170</v>
+        <v>632898</v>
       </c>
       <c r="R7" t="n">
-        <v>6898718</v>
+        <v>6898903</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1365,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664924</v>
+        <v>124664880</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1442,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633183</v>
+        <v>633177</v>
       </c>
       <c r="R8" t="n">
-        <v>6898714</v>
+        <v>6898718</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1514,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124664880</v>
+        <v>124676227</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79764</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,41 +1515,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633177</v>
+        <v>633194</v>
       </c>
       <c r="R9" t="n">
-        <v>6898718</v>
+        <v>6898707</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,19 +1579,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,6 +1595,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1626,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124665555</v>
+        <v>124665963</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>4772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,35 +1626,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1675,10 +1659,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633142</v>
+        <v>633052</v>
       </c>
       <c r="R10" t="n">
-        <v>6898840</v>
+        <v>6898874</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1710,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1704,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124676227</v>
+        <v>124664744</v>
       </c>
       <c r="B11" t="n">
-        <v>79764</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,40 +1747,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633194</v>
+        <v>633172</v>
       </c>
       <c r="R11" t="n">
-        <v>6898707</v>
+        <v>6898735</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,14 +1813,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,7 +1834,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1858,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664327</v>
+        <v>124664023</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,38 +1864,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633161</v>
+        <v>633092</v>
       </c>
       <c r="R12" t="n">
-        <v>6898722</v>
+        <v>6898802</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1933,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124666936</v>
+        <v>124667024</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,47 +1985,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632907</v>
+        <v>632896</v>
       </c>
       <c r="R13" t="n">
-        <v>6898900</v>
+        <v>6898908</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2054,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2064,7 +2058,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,6 +2069,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2091,7 +2105,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124664616</v>
+        <v>124663547</v>
       </c>
       <c r="B14" t="n">
         <v>74840</v>
@@ -2127,17 +2141,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633153</v>
+        <v>633000</v>
       </c>
       <c r="R14" t="n">
-        <v>6898758</v>
+        <v>6898916</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,7 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124663547</v>
+        <v>124666936</v>
       </c>
       <c r="B15" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,41 +2234,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633000</v>
+        <v>632907</v>
       </c>
       <c r="R15" t="n">
-        <v>6898916</v>
+        <v>6898900</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2278,7 +2306,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2288,12 +2316,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2320,10 +2343,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124665963</v>
+        <v>124664466</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2332,43 +2355,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100299</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633052</v>
+        <v>633170</v>
       </c>
       <c r="R16" t="n">
-        <v>6898874</v>
+        <v>6898718</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2400,7 +2418,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2428,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,10 +2455,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664023</v>
+        <v>124664616</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>74840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2453,43 +2471,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633092</v>
+        <v>633153</v>
       </c>
       <c r="R17" t="n">
-        <v>6898802</v>
+        <v>6898758</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2521,7 +2530,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2531,7 +2540,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2670,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124663369</v>
+        <v>124664327</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2682,47 +2691,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632999</v>
+        <v>633161</v>
       </c>
       <c r="R19" t="n">
-        <v>6898916</v>
+        <v>6898722</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,7 +2903,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124667201</v>
+        <v>124663369</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632898</v>
+        <v>632999</v>
       </c>
       <c r="R21" t="n">
-        <v>6898903</v>
+        <v>6898916</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1731,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124664744</v>
+        <v>124664023</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633172</v>
+        <v>633092</v>
       </c>
       <c r="R11" t="n">
-        <v>6898735</v>
+        <v>6898802</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664023</v>
+        <v>124664744</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,47 +1864,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633092</v>
+        <v>633172</v>
       </c>
       <c r="R12" t="n">
-        <v>6898802</v>
+        <v>6898735</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1731,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124664023</v>
+        <v>124664744</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633092</v>
+        <v>633172</v>
       </c>
       <c r="R11" t="n">
-        <v>6898802</v>
+        <v>6898735</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664744</v>
+        <v>124664023</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,47 +1864,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633172</v>
+        <v>633092</v>
       </c>
       <c r="R12" t="n">
-        <v>6898735</v>
+        <v>6898802</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664924</v>
+        <v>124665985</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,38 +937,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633183</v>
+        <v>633054</v>
       </c>
       <c r="R4" t="n">
-        <v>6898714</v>
+        <v>6898879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124665555</v>
+        <v>124664880</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,47 +1049,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633142</v>
+        <v>633177</v>
       </c>
       <c r="R5" t="n">
-        <v>6898840</v>
+        <v>6898718</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124667201</v>
+        <v>124663369</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1193,7 +1184,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1207,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632898</v>
+        <v>632999</v>
       </c>
       <c r="R6" t="n">
-        <v>6898903</v>
+        <v>6898916</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124667161</v>
+        <v>124663547</v>
       </c>
       <c r="B7" t="n">
-        <v>96445</v>
+        <v>74840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,25 +1282,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>990</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,13 +1310,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632898</v>
+        <v>633000</v>
       </c>
       <c r="R7" t="n">
-        <v>6898903</v>
+        <v>6898916</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664880</v>
+        <v>124664023</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,38 +1399,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633177</v>
+        <v>633092</v>
       </c>
       <c r="R8" t="n">
-        <v>6898718</v>
+        <v>6898802</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124676227</v>
+        <v>124667201</v>
       </c>
       <c r="B9" t="n">
-        <v>79764</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,40 +1524,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633194</v>
+        <v>632898</v>
       </c>
       <c r="R9" t="n">
-        <v>6898707</v>
+        <v>6898903</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,14 +1590,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,7 +1611,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1614,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124665963</v>
+        <v>124664616</v>
       </c>
       <c r="B10" t="n">
-        <v>4772</v>
+        <v>74840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,39 +1645,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633052</v>
+        <v>633153</v>
       </c>
       <c r="R10" t="n">
-        <v>6898874</v>
+        <v>6898758</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1694,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124664744</v>
+        <v>124664327</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,47 +1753,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633172</v>
+        <v>633161</v>
       </c>
       <c r="R11" t="n">
-        <v>6898735</v>
+        <v>6898722</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664023</v>
+        <v>124667161</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>96445</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,47 +1865,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633092</v>
+        <v>632898</v>
       </c>
       <c r="R12" t="n">
-        <v>6898802</v>
+        <v>6898903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1936,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124667024</v>
+        <v>124665963</v>
       </c>
       <c r="B13" t="n">
-        <v>96354</v>
+        <v>4772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,38 +1977,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632896</v>
+        <v>633052</v>
       </c>
       <c r="R13" t="n">
-        <v>6898908</v>
+        <v>6898874</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2048,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,7 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,26 +2066,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2105,10 +2082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124663547</v>
+        <v>124664924</v>
       </c>
       <c r="B14" t="n">
-        <v>74840</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,41 +2094,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633000</v>
+        <v>633183</v>
       </c>
       <c r="R14" t="n">
-        <v>6898916</v>
+        <v>6898714</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2180,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2167,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,7 +2194,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124666936</v>
+        <v>124663875</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2255,26 +2227,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632907</v>
+        <v>633040</v>
       </c>
       <c r="R15" t="n">
-        <v>6898900</v>
+        <v>6898800</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2306,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2316,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124664466</v>
+        <v>124667024</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,34 +2322,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633170</v>
+        <v>632896</v>
       </c>
       <c r="R16" t="n">
-        <v>6898718</v>
+        <v>6898908</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2418,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2428,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,6 +2402,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2455,10 +2438,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664616</v>
+        <v>124666936</v>
       </c>
       <c r="B17" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,38 +2450,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633153</v>
+        <v>632907</v>
       </c>
       <c r="R17" t="n">
-        <v>6898758</v>
+        <v>6898900</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2530,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2540,7 +2532,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2567,10 +2559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124665985</v>
+        <v>124676227</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>79764</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2579,41 +2571,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633054</v>
+        <v>633194</v>
       </c>
       <c r="R18" t="n">
-        <v>6898879</v>
+        <v>6898707</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2640,19 +2635,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:46</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,6 +2651,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2679,10 +2670,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124664327</v>
+        <v>124665555</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2691,38 +2682,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633161</v>
+        <v>633142</v>
       </c>
       <c r="R19" t="n">
-        <v>6898722</v>
+        <v>6898840</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,7 +2791,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124663875</v>
+        <v>124664744</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2824,17 +2824,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633040</v>
+        <v>633172</v>
       </c>
       <c r="R20" t="n">
-        <v>6898800</v>
+        <v>6898735</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2866,7 +2875,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2885,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,10 +2912,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124663369</v>
+        <v>124664466</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2915,47 +2924,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632999</v>
+        <v>633170</v>
       </c>
       <c r="R21" t="n">
-        <v>6898916</v>
+        <v>6898718</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124665985</v>
+        <v>124667161</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>96445</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633054</v>
+        <v>632898</v>
       </c>
       <c r="R4" t="n">
-        <v>6898879</v>
+        <v>6898903</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664880</v>
+        <v>124667024</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633177</v>
+        <v>632896</v>
       </c>
       <c r="R5" t="n">
-        <v>6898718</v>
+        <v>6898908</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,6 +1133,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,7 +1169,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124663369</v>
+        <v>124663875</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1182,26 +1202,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632999</v>
+        <v>633040</v>
       </c>
       <c r="R6" t="n">
-        <v>6898916</v>
+        <v>6898800</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124663547</v>
+        <v>124665985</v>
       </c>
       <c r="B7" t="n">
-        <v>74840</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1297,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,13 +1321,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633000</v>
+        <v>633054</v>
       </c>
       <c r="R7" t="n">
-        <v>6898916</v>
+        <v>6898879</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664023</v>
+        <v>124664744</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,47 +1405,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633092</v>
+        <v>633172</v>
       </c>
       <c r="R8" t="n">
-        <v>6898802</v>
+        <v>6898735</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124667201</v>
+        <v>124664880</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,47 +1526,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632898</v>
+        <v>633177</v>
       </c>
       <c r="R9" t="n">
-        <v>6898903</v>
+        <v>6898718</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1592,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1626,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124664616</v>
+        <v>124663547</v>
       </c>
       <c r="B10" t="n">
         <v>74840</v>
@@ -1665,17 +1662,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633153</v>
+        <v>633000</v>
       </c>
       <c r="R10" t="n">
-        <v>6898758</v>
+        <v>6898916</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1711,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1853,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124667161</v>
+        <v>124663369</v>
       </c>
       <c r="B12" t="n">
-        <v>96445</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,34 +1871,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>990</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632898</v>
+        <v>632999</v>
       </c>
       <c r="R12" t="n">
-        <v>6898903</v>
+        <v>6898916</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1928,7 +1939,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,7 +1949,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124665963</v>
+        <v>124664616</v>
       </c>
       <c r="B13" t="n">
-        <v>4772</v>
+        <v>74840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,39 +1992,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633052</v>
+        <v>633153</v>
       </c>
       <c r="R13" t="n">
-        <v>6898874</v>
+        <v>6898758</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2045,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2061,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124664924</v>
+        <v>124664023</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,38 +2100,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633183</v>
+        <v>633092</v>
       </c>
       <c r="R14" t="n">
-        <v>6898714</v>
+        <v>6898802</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2172,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,7 +2182,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124663875</v>
+        <v>124664924</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,38 +2221,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633040</v>
+        <v>633183</v>
       </c>
       <c r="R15" t="n">
-        <v>6898800</v>
+        <v>6898714</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2269,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124667024</v>
+        <v>124667201</v>
       </c>
       <c r="B16" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,38 +2333,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632896</v>
+        <v>632898</v>
       </c>
       <c r="R16" t="n">
-        <v>6898908</v>
+        <v>6898903</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2381,7 +2405,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2415,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,26 +2426,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2438,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124666936</v>
+        <v>124664466</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2450,47 +2454,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632907</v>
+        <v>633170</v>
       </c>
       <c r="R17" t="n">
-        <v>6898900</v>
+        <v>6898718</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2522,7 +2517,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,7 +2527,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2670,7 +2665,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124665555</v>
+        <v>124666936</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2719,10 +2714,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633142</v>
+        <v>632907</v>
       </c>
       <c r="R19" t="n">
-        <v>6898840</v>
+        <v>6898900</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2754,7 +2749,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2759,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,10 +2786,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124664744</v>
+        <v>124665963</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>4772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,47 +2798,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633172</v>
+        <v>633052</v>
       </c>
       <c r="R20" t="n">
-        <v>6898735</v>
+        <v>6898874</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2875,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2885,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2912,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124664466</v>
+        <v>124665555</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2924,38 +2915,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633170</v>
+        <v>633142</v>
       </c>
       <c r="R21" t="n">
-        <v>6898718</v>
+        <v>6898840</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -2554,10 +2554,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124676227</v>
+        <v>124666936</v>
       </c>
       <c r="B18" t="n">
-        <v>79764</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2570,40 +2570,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633194</v>
+        <v>632907</v>
       </c>
       <c r="R18" t="n">
-        <v>6898707</v>
+        <v>6898900</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2630,14 +2636,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,7 +2657,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2665,10 +2675,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124666936</v>
+        <v>124676227</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>79764</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2681,46 +2691,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632907</v>
+        <v>633194</v>
       </c>
       <c r="R19" t="n">
-        <v>6898900</v>
+        <v>6898707</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2747,19 +2751,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:10</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,6 +2767,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667161</v>
+        <v>124666936</v>
       </c>
       <c r="B4" t="n">
-        <v>96445</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,34 +941,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>990</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632898</v>
+        <v>632907</v>
       </c>
       <c r="R4" t="n">
-        <v>6898903</v>
+        <v>6898900</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124667024</v>
+        <v>124663369</v>
       </c>
       <c r="B5" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,38 +1058,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632896</v>
+        <v>632999</v>
       </c>
       <c r="R5" t="n">
-        <v>6898908</v>
+        <v>6898916</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,26 +1151,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1169,7 +1167,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124663875</v>
+        <v>124665555</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1202,17 +1200,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633040</v>
+        <v>633142</v>
       </c>
       <c r="R6" t="n">
-        <v>6898800</v>
+        <v>6898840</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,7 +1251,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1261,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124665985</v>
+        <v>124667161</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>96445</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,25 +1300,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633054</v>
+        <v>632898</v>
       </c>
       <c r="R7" t="n">
-        <v>6898879</v>
+        <v>6898903</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664744</v>
+        <v>124664023</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,47 +1412,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633172</v>
+        <v>633092</v>
       </c>
       <c r="R8" t="n">
-        <v>6898735</v>
+        <v>6898802</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1477,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124664880</v>
+        <v>124664327</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,21 +1537,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1554,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633177</v>
+        <v>633161</v>
       </c>
       <c r="R9" t="n">
-        <v>6898718</v>
+        <v>6898722</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,7 +1633,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124663547</v>
+        <v>124664616</v>
       </c>
       <c r="B10" t="n">
         <v>74840</v>
@@ -1662,17 +1669,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633000</v>
+        <v>633153</v>
       </c>
       <c r="R10" t="n">
-        <v>6898916</v>
+        <v>6898758</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,12 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124664327</v>
+        <v>124664466</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1783,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633161</v>
+        <v>633170</v>
       </c>
       <c r="R11" t="n">
-        <v>6898722</v>
+        <v>6898718</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1818,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124663369</v>
+        <v>124664880</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,47 +1869,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632999</v>
+        <v>633177</v>
       </c>
       <c r="R12" t="n">
-        <v>6898916</v>
+        <v>6898718</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1939,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1949,7 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124664616</v>
+        <v>124664924</v>
       </c>
       <c r="B13" t="n">
-        <v>74840</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,25 +1981,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2016,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633153</v>
+        <v>633183</v>
       </c>
       <c r="R13" t="n">
-        <v>6898758</v>
+        <v>6898714</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2051,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2061,7 +2054,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124664023</v>
+        <v>124663547</v>
       </c>
       <c r="B14" t="n">
-        <v>100279</v>
+        <v>74840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,46 +2097,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633092</v>
+        <v>633000</v>
       </c>
       <c r="R14" t="n">
-        <v>6898802</v>
+        <v>6898916</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2172,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2182,7 +2166,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124664924</v>
+        <v>124663875</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,38 +2210,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633183</v>
+        <v>633040</v>
       </c>
       <c r="R15" t="n">
-        <v>6898714</v>
+        <v>6898800</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2284,7 +2273,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2283,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2321,7 +2310,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124667201</v>
+        <v>124664744</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2356,7 +2345,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2366,14 +2355,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632898</v>
+        <v>633172</v>
       </c>
       <c r="R16" t="n">
-        <v>6898903</v>
+        <v>6898735</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2405,7 +2394,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2415,7 +2404,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664466</v>
+        <v>124667201</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,38 +2443,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633170</v>
+        <v>632898</v>
       </c>
       <c r="R17" t="n">
-        <v>6898718</v>
+        <v>6898903</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2517,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2527,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124666936</v>
+        <v>124665985</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2566,47 +2564,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632907</v>
+        <v>633054</v>
       </c>
       <c r="R18" t="n">
-        <v>6898900</v>
+        <v>6898879</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2638,7 +2627,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2648,7 +2637,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,10 +2775,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124665963</v>
+        <v>124667024</v>
       </c>
       <c r="B20" t="n">
-        <v>4772</v>
+        <v>96354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2798,43 +2787,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633052</v>
+        <v>632896</v>
       </c>
       <c r="R20" t="n">
-        <v>6898874</v>
+        <v>6898908</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2866,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,6 +2871,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2903,10 +2907,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124665555</v>
+        <v>124665963</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>4772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2915,35 +2919,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633142</v>
+        <v>633052</v>
       </c>
       <c r="R21" t="n">
-        <v>6898840</v>
+        <v>6898874</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -2081,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124663547</v>
+        <v>124663875</v>
       </c>
       <c r="B14" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,25 +2093,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633000</v>
+        <v>633040</v>
       </c>
       <c r="R14" t="n">
-        <v>6898916</v>
+        <v>6898800</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,12 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,7 +2193,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124663875</v>
+        <v>124664744</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2231,17 +2226,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633040</v>
+        <v>633172</v>
       </c>
       <c r="R15" t="n">
-        <v>6898800</v>
+        <v>6898735</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2273,7 +2277,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2283,7 +2287,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124664744</v>
+        <v>124663547</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,50 +2326,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633172</v>
+        <v>633000</v>
       </c>
       <c r="R16" t="n">
-        <v>6898735</v>
+        <v>6898916</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2394,7 +2389,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2404,7 +2399,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124666936</v>
+        <v>124667201</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632907</v>
+        <v>632898</v>
       </c>
       <c r="R4" t="n">
-        <v>6898900</v>
+        <v>6898903</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124663369</v>
+        <v>124664880</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,47 +1058,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632999</v>
+        <v>633177</v>
       </c>
       <c r="R5" t="n">
-        <v>6898916</v>
+        <v>6898718</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1130,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124665555</v>
+        <v>124676227</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,46 +1174,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633142</v>
+        <v>633194</v>
       </c>
       <c r="R6" t="n">
-        <v>6898840</v>
+        <v>6898707</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,19 +1234,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:35</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,6 +1250,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1288,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124667161</v>
+        <v>124664466</v>
       </c>
       <c r="B7" t="n">
-        <v>96445</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,38 +1281,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>990</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632898</v>
+        <v>633170</v>
       </c>
       <c r="R7" t="n">
-        <v>6898903</v>
+        <v>6898718</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1363,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664023</v>
+        <v>124663875</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,47 +1393,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633092</v>
+        <v>633040</v>
       </c>
       <c r="R8" t="n">
-        <v>6898802</v>
+        <v>6898800</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1521,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124664327</v>
+        <v>124664744</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,38 +1505,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633161</v>
+        <v>633172</v>
       </c>
       <c r="R9" t="n">
-        <v>6898722</v>
+        <v>6898735</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,7 +1614,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124664616</v>
+        <v>124663547</v>
       </c>
       <c r="B10" t="n">
         <v>74840</v>
@@ -1669,17 +1650,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633153</v>
+        <v>633000</v>
       </c>
       <c r="R10" t="n">
-        <v>6898758</v>
+        <v>6898916</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1699,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124664466</v>
+        <v>124663369</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,38 +1743,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633170</v>
+        <v>632999</v>
       </c>
       <c r="R11" t="n">
-        <v>6898718</v>
+        <v>6898916</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664880</v>
+        <v>124665963</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>4772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,38 +1864,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633177</v>
+        <v>633052</v>
       </c>
       <c r="R12" t="n">
-        <v>6898718</v>
+        <v>6898874</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124664924</v>
+        <v>124664023</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,38 +1981,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633183</v>
+        <v>633092</v>
       </c>
       <c r="R13" t="n">
-        <v>6898714</v>
+        <v>6898802</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2044,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,7 +2063,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124663875</v>
+        <v>124664924</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,38 +2102,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633040</v>
+        <v>633183</v>
       </c>
       <c r="R14" t="n">
-        <v>6898800</v>
+        <v>6898714</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2156,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,10 +2202,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124664744</v>
+        <v>124667161</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>96445</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,43 +2218,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633172</v>
+        <v>632898</v>
       </c>
       <c r="R15" t="n">
-        <v>6898735</v>
+        <v>6898903</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124663547</v>
+        <v>124666936</v>
       </c>
       <c r="B16" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,41 +2326,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633000</v>
+        <v>632907</v>
       </c>
       <c r="R16" t="n">
-        <v>6898916</v>
+        <v>6898900</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2389,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2399,12 +2408,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124667201</v>
+        <v>124667024</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,47 +2447,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632898</v>
+        <v>632896</v>
       </c>
       <c r="R17" t="n">
-        <v>6898903</v>
+        <v>6898908</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2515,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,7 +2520,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,6 +2531,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2552,10 +2567,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124665985</v>
+        <v>124664327</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,38 +2579,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633054</v>
+        <v>633161</v>
       </c>
       <c r="R18" t="n">
-        <v>6898879</v>
+        <v>6898722</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2627,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2637,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124676227</v>
+        <v>124664616</v>
       </c>
       <c r="B19" t="n">
-        <v>79764</v>
+        <v>74840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2676,44 +2691,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>392</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633194</v>
+        <v>633153</v>
       </c>
       <c r="R19" t="n">
-        <v>6898707</v>
+        <v>6898758</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2740,14 +2752,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,7 +2773,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2775,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124667024</v>
+        <v>124665985</v>
       </c>
       <c r="B20" t="n">
-        <v>96354</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2787,25 +2803,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2815,10 +2831,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>632896</v>
+        <v>633054</v>
       </c>
       <c r="R20" t="n">
-        <v>6898908</v>
+        <v>6898879</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2850,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2871,26 +2887,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2907,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124665963</v>
+        <v>124665555</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2919,31 +2915,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633052</v>
+        <v>633142</v>
       </c>
       <c r="R21" t="n">
-        <v>6898874</v>
+        <v>6898840</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667201</v>
+        <v>124663547</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,50 +937,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632898</v>
+        <v>633000</v>
       </c>
       <c r="R4" t="n">
-        <v>6898903</v>
+        <v>6898916</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664880</v>
+        <v>124664327</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,21 +1058,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633177</v>
+        <v>633161</v>
       </c>
       <c r="R5" t="n">
-        <v>6898718</v>
+        <v>6898722</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124676227</v>
+        <v>124666936</v>
       </c>
       <c r="B6" t="n">
-        <v>79764</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,40 +1170,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633194</v>
+        <v>632907</v>
       </c>
       <c r="R6" t="n">
-        <v>6898707</v>
+        <v>6898900</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,14 +1236,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1257,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124664466</v>
+        <v>124664744</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,38 +1287,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633170</v>
+        <v>633172</v>
       </c>
       <c r="R7" t="n">
-        <v>6898718</v>
+        <v>6898735</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124663875</v>
+        <v>124667024</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,25 +1408,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633040</v>
+        <v>632896</v>
       </c>
       <c r="R8" t="n">
-        <v>6898800</v>
+        <v>6898908</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,6 +1492,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1493,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124664744</v>
+        <v>124664924</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,47 +1540,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633172</v>
+        <v>633183</v>
       </c>
       <c r="R9" t="n">
-        <v>6898735</v>
+        <v>6898714</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1614,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124663547</v>
+        <v>124664023</v>
       </c>
       <c r="B10" t="n">
-        <v>74840</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,37 +1656,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633000</v>
+        <v>633092</v>
       </c>
       <c r="R10" t="n">
-        <v>6898916</v>
+        <v>6898802</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,7 +1724,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,12 +1734,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,10 +1761,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124663369</v>
+        <v>124665963</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>4772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,35 +1773,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1780,10 +1806,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632999</v>
+        <v>633052</v>
       </c>
       <c r="R11" t="n">
-        <v>6898916</v>
+        <v>6898874</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,7 +1841,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1851,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1878,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124665963</v>
+        <v>124665985</v>
       </c>
       <c r="B12" t="n">
-        <v>4772</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,39 +1894,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633052</v>
+        <v>633054</v>
       </c>
       <c r="R12" t="n">
-        <v>6898874</v>
+        <v>6898879</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1969,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124664023</v>
+        <v>124667201</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,35 +2002,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2018,10 +2039,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633092</v>
+        <v>632898</v>
       </c>
       <c r="R13" t="n">
-        <v>6898802</v>
+        <v>6898903</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2053,7 +2074,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,7 +2084,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,10 +2111,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124664924</v>
+        <v>124664880</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2106,21 +2127,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633183</v>
+        <v>633177</v>
       </c>
       <c r="R14" t="n">
-        <v>6898714</v>
+        <v>6898718</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2202,10 +2223,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124667161</v>
+        <v>124664466</v>
       </c>
       <c r="B15" t="n">
-        <v>96445</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,38 +2235,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>990</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632898</v>
+        <v>633170</v>
       </c>
       <c r="R15" t="n">
-        <v>6898903</v>
+        <v>6898718</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2277,7 +2298,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2287,7 +2308,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,7 +2335,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124666936</v>
+        <v>124663369</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2349,7 +2370,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2363,10 +2384,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632907</v>
+        <v>632999</v>
       </c>
       <c r="R16" t="n">
-        <v>6898900</v>
+        <v>6898916</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2398,7 +2419,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,7 +2429,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,10 +2456,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124667024</v>
+        <v>124664616</v>
       </c>
       <c r="B17" t="n">
-        <v>96354</v>
+        <v>74840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,38 +2468,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632896</v>
+        <v>633153</v>
       </c>
       <c r="R17" t="n">
-        <v>6898908</v>
+        <v>6898758</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2510,7 +2531,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,7 +2541,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,26 +2552,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2567,10 +2568,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124664327</v>
+        <v>124667161</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>96445</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2579,38 +2580,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>990</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633161</v>
+        <v>632898</v>
       </c>
       <c r="R18" t="n">
-        <v>6898722</v>
+        <v>6898903</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2642,7 +2643,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2653,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124664616</v>
+        <v>124663875</v>
       </c>
       <c r="B19" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2691,38 +2692,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633153</v>
+        <v>633040</v>
       </c>
       <c r="R19" t="n">
-        <v>6898758</v>
+        <v>6898800</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2754,7 +2755,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2765,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,10 +2792,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124665985</v>
+        <v>124676227</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>79764</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,41 +2804,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633054</v>
+        <v>633194</v>
       </c>
       <c r="R20" t="n">
-        <v>6898879</v>
+        <v>6898707</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2864,19 +2868,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:46</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,6 +2884,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124663547</v>
+        <v>124666936</v>
       </c>
       <c r="B4" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,41 +937,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633000</v>
+        <v>632907</v>
       </c>
       <c r="R4" t="n">
-        <v>6898916</v>
+        <v>6898900</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,12 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664327</v>
+        <v>124663547</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>74840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,41 +1058,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633161</v>
+        <v>633000</v>
       </c>
       <c r="R5" t="n">
-        <v>6898722</v>
+        <v>6898916</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124666936</v>
+        <v>124664327</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,47 +1175,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632907</v>
+        <v>633161</v>
       </c>
       <c r="R6" t="n">
-        <v>6898900</v>
+        <v>6898722</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124666936</v>
+        <v>124664466</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,47 +937,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632907</v>
+        <v>633170</v>
       </c>
       <c r="R4" t="n">
-        <v>6898900</v>
+        <v>6898718</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124663547</v>
+        <v>124665963</v>
       </c>
       <c r="B5" t="n">
-        <v>74840</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,37 +1053,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633000</v>
+        <v>633052</v>
       </c>
       <c r="R5" t="n">
-        <v>6898916</v>
+        <v>6898874</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124664327</v>
+        <v>124676227</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,41 +1166,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633161</v>
+        <v>633194</v>
       </c>
       <c r="R6" t="n">
-        <v>6898722</v>
+        <v>6898707</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,19 +1230,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:57</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,6 +1246,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1275,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124664744</v>
+        <v>124667161</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>96445</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,43 +1281,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633172</v>
+        <v>632898</v>
       </c>
       <c r="R7" t="n">
-        <v>6898735</v>
+        <v>6898903</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1359,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124667024</v>
+        <v>124664924</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,34 +1393,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632896</v>
+        <v>633183</v>
       </c>
       <c r="R8" t="n">
-        <v>6898908</v>
+        <v>6898714</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,26 +1473,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1528,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124664924</v>
+        <v>124663875</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,38 +1501,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633183</v>
+        <v>633040</v>
       </c>
       <c r="R9" t="n">
-        <v>6898714</v>
+        <v>6898800</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124664023</v>
+        <v>124666936</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,35 +1613,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1689,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633092</v>
+        <v>632907</v>
       </c>
       <c r="R10" t="n">
-        <v>6898802</v>
+        <v>6898900</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1724,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1734,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124665963</v>
+        <v>124667024</v>
       </c>
       <c r="B11" t="n">
-        <v>4772</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,43 +1734,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633052</v>
+        <v>632896</v>
       </c>
       <c r="R11" t="n">
-        <v>6898874</v>
+        <v>6898908</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1841,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1851,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,6 +1818,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1878,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124665985</v>
+        <v>124664880</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,38 +1866,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633054</v>
+        <v>633177</v>
       </c>
       <c r="R12" t="n">
-        <v>6898879</v>
+        <v>6898718</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1953,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1963,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124667201</v>
+        <v>124664327</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,47 +1978,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632898</v>
+        <v>633161</v>
       </c>
       <c r="R13" t="n">
-        <v>6898903</v>
+        <v>6898722</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2074,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2084,7 +2051,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2111,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124664880</v>
+        <v>124667201</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,38 +2090,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633177</v>
+        <v>632898</v>
       </c>
       <c r="R14" t="n">
-        <v>6898718</v>
+        <v>6898903</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2186,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2172,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124664466</v>
+        <v>124665985</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2235,38 +2211,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633170</v>
+        <v>633054</v>
       </c>
       <c r="R15" t="n">
-        <v>6898718</v>
+        <v>6898879</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2298,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2308,7 +2284,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2568,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124667161</v>
+        <v>124663547</v>
       </c>
       <c r="B18" t="n">
-        <v>96445</v>
+        <v>74840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,25 +2556,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>990</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2608,13 +2584,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632898</v>
+        <v>633000</v>
       </c>
       <c r="R18" t="n">
-        <v>6898903</v>
+        <v>6898916</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2643,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2653,7 +2629,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2680,10 +2661,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124663875</v>
+        <v>124664023</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,38 +2673,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633040</v>
+        <v>633092</v>
       </c>
       <c r="R19" t="n">
-        <v>6898800</v>
+        <v>6898802</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2792,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124676227</v>
+        <v>124665555</v>
       </c>
       <c r="B20" t="n">
-        <v>79764</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2808,40 +2798,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633194</v>
+        <v>633142</v>
       </c>
       <c r="R20" t="n">
-        <v>6898707</v>
+        <v>6898840</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2868,14 +2864,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,7 +2885,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124665555</v>
+        <v>124664744</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2948,14 +2948,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633142</v>
+        <v>633172</v>
       </c>
       <c r="R21" t="n">
-        <v>6898840</v>
+        <v>6898735</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664466</v>
+        <v>124664616</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>74840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633170</v>
+        <v>633153</v>
       </c>
       <c r="R4" t="n">
-        <v>6898718</v>
+        <v>6898758</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124665963</v>
+        <v>124664466</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,43 +1049,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633052</v>
+        <v>633170</v>
       </c>
       <c r="R5" t="n">
-        <v>6898874</v>
+        <v>6898718</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124676227</v>
+        <v>124667201</v>
       </c>
       <c r="B6" t="n">
-        <v>79764</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,40 +1165,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633194</v>
+        <v>632898</v>
       </c>
       <c r="R6" t="n">
-        <v>6898707</v>
+        <v>6898903</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,14 +1231,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,7 +1252,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1265,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124667161</v>
+        <v>124666936</v>
       </c>
       <c r="B7" t="n">
-        <v>96445</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,34 +1286,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>990</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632898</v>
+        <v>632907</v>
       </c>
       <c r="R7" t="n">
-        <v>6898903</v>
+        <v>6898900</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664924</v>
+        <v>124664023</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,38 +1403,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633183</v>
+        <v>633092</v>
       </c>
       <c r="R8" t="n">
-        <v>6898714</v>
+        <v>6898802</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124663875</v>
+        <v>124663547</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,25 +1524,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,13 +1552,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633040</v>
+        <v>633000</v>
       </c>
       <c r="R9" t="n">
-        <v>6898800</v>
+        <v>6898916</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1597,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1629,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124666936</v>
+        <v>124663875</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1634,26 +1662,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632907</v>
+        <v>633040</v>
       </c>
       <c r="R10" t="n">
-        <v>6898900</v>
+        <v>6898800</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124667024</v>
+        <v>124663369</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,38 +1753,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632896</v>
+        <v>632999</v>
       </c>
       <c r="R11" t="n">
-        <v>6898908</v>
+        <v>6898916</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1835,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,26 +1846,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1854,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664880</v>
+        <v>124676227</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79764</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,41 +1874,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633177</v>
+        <v>633194</v>
       </c>
       <c r="R12" t="n">
-        <v>6898718</v>
+        <v>6898707</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,19 +1938,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,6 +1954,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124664327</v>
+        <v>124667024</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,34 +1989,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633161</v>
+        <v>632896</v>
       </c>
       <c r="R13" t="n">
-        <v>6898722</v>
+        <v>6898908</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2041,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,7 +2058,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,6 +2069,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2078,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124667201</v>
+        <v>124667161</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>96445</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,33 +2121,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
@@ -2162,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2190,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124665985</v>
+        <v>124664744</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,38 +2229,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633054</v>
+        <v>633172</v>
       </c>
       <c r="R15" t="n">
-        <v>6898879</v>
+        <v>6898735</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2274,7 +2301,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,7 +2311,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124663369</v>
+        <v>124664880</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,47 +2350,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632999</v>
+        <v>633177</v>
       </c>
       <c r="R16" t="n">
-        <v>6898916</v>
+        <v>6898718</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2395,7 +2413,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,7 +2423,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,10 +2450,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664616</v>
+        <v>124665555</v>
       </c>
       <c r="B17" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2444,38 +2462,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633153</v>
+        <v>633142</v>
       </c>
       <c r="R17" t="n">
-        <v>6898758</v>
+        <v>6898840</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2507,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,7 +2544,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,10 +2571,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124663547</v>
+        <v>124664327</v>
       </c>
       <c r="B18" t="n">
-        <v>74840</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2556,41 +2583,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633000</v>
+        <v>633161</v>
       </c>
       <c r="R18" t="n">
-        <v>6898916</v>
+        <v>6898722</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2619,7 +2646,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,12 +2656,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,10 +2683,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124664023</v>
+        <v>124665963</v>
       </c>
       <c r="B19" t="n">
-        <v>100279</v>
+        <v>4772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2677,31 +2699,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2710,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633092</v>
+        <v>633052</v>
       </c>
       <c r="R19" t="n">
-        <v>6898802</v>
+        <v>6898874</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2745,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2755,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,10 +2800,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124665555</v>
+        <v>124665985</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,47 +2812,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633142</v>
+        <v>633054</v>
       </c>
       <c r="R20" t="n">
-        <v>6898840</v>
+        <v>6898879</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2866,7 +2875,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2885,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,10 +2912,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124664744</v>
+        <v>124664924</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2915,47 +2924,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633172</v>
+        <v>633183</v>
       </c>
       <c r="R21" t="n">
-        <v>6898735</v>
+        <v>6898714</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664616</v>
+        <v>124664327</v>
       </c>
       <c r="B4" t="n">
-        <v>74840</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633153</v>
+        <v>633161</v>
       </c>
       <c r="R4" t="n">
-        <v>6898758</v>
+        <v>6898722</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664466</v>
+        <v>124664023</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,38 +1049,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633170</v>
+        <v>633092</v>
       </c>
       <c r="R5" t="n">
-        <v>6898718</v>
+        <v>6898802</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124667201</v>
+        <v>124664880</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,47 +1170,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632898</v>
+        <v>633177</v>
       </c>
       <c r="R6" t="n">
-        <v>6898903</v>
+        <v>6898718</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124666936</v>
+        <v>124665985</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,47 +1282,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632907</v>
+        <v>633054</v>
       </c>
       <c r="R7" t="n">
-        <v>6898900</v>
+        <v>6898879</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664023</v>
+        <v>124665963</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>4772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,31 +1398,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1440,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633092</v>
+        <v>633052</v>
       </c>
       <c r="R8" t="n">
-        <v>6898802</v>
+        <v>6898874</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124663547</v>
+        <v>124664744</v>
       </c>
       <c r="B9" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,41 +1511,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633000</v>
+        <v>633172</v>
       </c>
       <c r="R9" t="n">
-        <v>6898916</v>
+        <v>6898735</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,12 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124663875</v>
+        <v>124664466</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,38 +1632,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633040</v>
+        <v>633170</v>
       </c>
       <c r="R10" t="n">
-        <v>6898800</v>
+        <v>6898718</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124663369</v>
+        <v>124676227</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79764</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,46 +1748,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632999</v>
+        <v>633194</v>
       </c>
       <c r="R11" t="n">
-        <v>6898916</v>
+        <v>6898707</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,19 +1808,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,6 +1824,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1862,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124676227</v>
+        <v>124667161</v>
       </c>
       <c r="B12" t="n">
-        <v>79764</v>
+        <v>96445</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,40 +1859,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>392</v>
+        <v>990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633194</v>
+        <v>632898</v>
       </c>
       <c r="R12" t="n">
-        <v>6898707</v>
+        <v>6898903</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,14 +1916,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,7 +1937,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1973,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124667024</v>
+        <v>124664616</v>
       </c>
       <c r="B13" t="n">
-        <v>96354</v>
+        <v>74840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,38 +1967,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632896</v>
+        <v>633153</v>
       </c>
       <c r="R13" t="n">
-        <v>6898908</v>
+        <v>6898758</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2048,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,26 +2051,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2105,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124667161</v>
+        <v>124664924</v>
       </c>
       <c r="B14" t="n">
-        <v>96445</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,38 +2079,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>990</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632898</v>
+        <v>633183</v>
       </c>
       <c r="R14" t="n">
-        <v>6898903</v>
+        <v>6898714</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2180,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,7 +2179,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124664744</v>
+        <v>124666936</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2252,7 +2214,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2262,14 +2224,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633172</v>
+        <v>632907</v>
       </c>
       <c r="R15" t="n">
-        <v>6898735</v>
+        <v>6898900</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2301,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2311,7 +2273,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2338,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124664880</v>
+        <v>124667201</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2350,38 +2312,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633177</v>
+        <v>632898</v>
       </c>
       <c r="R16" t="n">
-        <v>6898718</v>
+        <v>6898903</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2413,7 +2384,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2423,7 +2394,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2450,10 +2421,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124665555</v>
+        <v>124667024</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2462,47 +2433,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633142</v>
+        <v>632896</v>
       </c>
       <c r="R17" t="n">
-        <v>6898840</v>
+        <v>6898908</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2534,7 +2496,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,7 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,6 +2517,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2571,10 +2553,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124664327</v>
+        <v>124663547</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>74840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,41 +2565,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633161</v>
+        <v>633000</v>
       </c>
       <c r="R18" t="n">
-        <v>6898722</v>
+        <v>6898916</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2646,7 +2628,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2656,7 +2638,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,10 +2670,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124665963</v>
+        <v>124665555</v>
       </c>
       <c r="B19" t="n">
-        <v>4772</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2695,31 +2682,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2728,10 +2719,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633052</v>
+        <v>633142</v>
       </c>
       <c r="R19" t="n">
-        <v>6898874</v>
+        <v>6898840</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2763,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2800,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124665985</v>
+        <v>124663875</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2812,25 +2803,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2840,10 +2831,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633054</v>
+        <v>633040</v>
       </c>
       <c r="R20" t="n">
-        <v>6898879</v>
+        <v>6898800</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2875,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2885,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2912,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124664924</v>
+        <v>124663369</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2924,38 +2915,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633183</v>
+        <v>632999</v>
       </c>
       <c r="R21" t="n">
-        <v>6898714</v>
+        <v>6898916</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664327</v>
+        <v>124664616</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>74840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633161</v>
+        <v>633153</v>
       </c>
       <c r="R4" t="n">
-        <v>6898722</v>
+        <v>6898758</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664023</v>
+        <v>124667161</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>96445</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,47 +1049,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633092</v>
+        <v>632898</v>
       </c>
       <c r="R5" t="n">
-        <v>6898802</v>
+        <v>6898903</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124664880</v>
+        <v>124676227</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,41 +1161,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633177</v>
+        <v>633194</v>
       </c>
       <c r="R6" t="n">
-        <v>6898718</v>
+        <v>6898707</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,19 +1225,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,6 +1241,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124665985</v>
+        <v>124665963</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633054</v>
+        <v>633052</v>
       </c>
       <c r="R7" t="n">
-        <v>6898879</v>
+        <v>6898874</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124665963</v>
+        <v>124663369</v>
       </c>
       <c r="B8" t="n">
-        <v>4772</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,31 +1389,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1427,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633052</v>
+        <v>632999</v>
       </c>
       <c r="R8" t="n">
-        <v>6898874</v>
+        <v>6898916</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1462,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,7 +1498,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124664744</v>
+        <v>124665555</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1534,7 +1533,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1544,14 +1543,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633172</v>
+        <v>633142</v>
       </c>
       <c r="R9" t="n">
-        <v>6898735</v>
+        <v>6898840</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1583,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124664466</v>
+        <v>124664023</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,38 +1631,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633170</v>
+        <v>633092</v>
       </c>
       <c r="R10" t="n">
-        <v>6898718</v>
+        <v>6898802</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1695,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1713,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124676227</v>
+        <v>124667024</v>
       </c>
       <c r="B11" t="n">
-        <v>79764</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,44 +1752,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633194</v>
+        <v>632896</v>
       </c>
       <c r="R11" t="n">
-        <v>6898707</v>
+        <v>6898908</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,14 +1813,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,9 +1834,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1843,10 +1872,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124667161</v>
+        <v>124663547</v>
       </c>
       <c r="B12" t="n">
-        <v>96445</v>
+        <v>74840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,25 +1884,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>990</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,13 +1912,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632898</v>
+        <v>633000</v>
       </c>
       <c r="R12" t="n">
-        <v>6898903</v>
+        <v>6898916</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1918,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1957,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,10 +1989,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124664616</v>
+        <v>124664924</v>
       </c>
       <c r="B13" t="n">
-        <v>74840</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,25 +2001,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1995,10 +2029,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633153</v>
+        <v>633183</v>
       </c>
       <c r="R13" t="n">
-        <v>6898758</v>
+        <v>6898714</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2030,7 +2064,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2074,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,10 +2101,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124664924</v>
+        <v>124664744</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,38 +2113,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633183</v>
+        <v>633172</v>
       </c>
       <c r="R14" t="n">
-        <v>6898714</v>
+        <v>6898735</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2179,7 +2222,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124666936</v>
+        <v>124667201</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2214,7 +2257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2228,10 +2271,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632907</v>
+        <v>632898</v>
       </c>
       <c r="R15" t="n">
-        <v>6898900</v>
+        <v>6898903</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2263,7 +2306,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2316,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,10 +2343,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124667201</v>
+        <v>124664327</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,47 +2355,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632898</v>
+        <v>633161</v>
       </c>
       <c r="R16" t="n">
-        <v>6898903</v>
+        <v>6898722</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2384,7 +2418,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,7 +2428,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,10 +2455,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124667024</v>
+        <v>124664880</v>
       </c>
       <c r="B17" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,34 +2471,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632896</v>
+        <v>633177</v>
       </c>
       <c r="R17" t="n">
-        <v>6898908</v>
+        <v>6898718</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2496,7 +2530,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2506,7 +2540,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,26 +2551,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2553,10 +2567,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124663547</v>
+        <v>124665985</v>
       </c>
       <c r="B18" t="n">
-        <v>74840</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2569,21 +2583,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2593,13 +2607,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633000</v>
+        <v>633054</v>
       </c>
       <c r="R18" t="n">
-        <v>6898916</v>
+        <v>6898879</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2628,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2638,12 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124665555</v>
+        <v>124664466</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2682,47 +2691,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633142</v>
+        <v>633170</v>
       </c>
       <c r="R19" t="n">
-        <v>6898840</v>
+        <v>6898718</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,7 +2903,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124663369</v>
+        <v>124666936</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632999</v>
+        <v>632907</v>
       </c>
       <c r="R21" t="n">
-        <v>6898916</v>
+        <v>6898900</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664616</v>
+        <v>124664744</v>
       </c>
       <c r="B4" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,38 +937,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633153</v>
+        <v>633172</v>
       </c>
       <c r="R4" t="n">
-        <v>6898758</v>
+        <v>6898735</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124667161</v>
+        <v>124664466</v>
       </c>
       <c r="B5" t="n">
-        <v>96445</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,38 +1058,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>990</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632898</v>
+        <v>633170</v>
       </c>
       <c r="R5" t="n">
-        <v>6898903</v>
+        <v>6898718</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124676227</v>
+        <v>124664924</v>
       </c>
       <c r="B6" t="n">
-        <v>79764</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,44 +1170,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>392</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633194</v>
+        <v>633183</v>
       </c>
       <c r="R6" t="n">
-        <v>6898707</v>
+        <v>6898714</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,14 +1231,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,7 +1252,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124665963</v>
+        <v>124667201</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,31 +1282,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633052</v>
+        <v>632898</v>
       </c>
       <c r="R7" t="n">
-        <v>6898874</v>
+        <v>6898903</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124663369</v>
+        <v>124664023</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,35 +1403,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632999</v>
+        <v>633092</v>
       </c>
       <c r="R8" t="n">
-        <v>6898916</v>
+        <v>6898802</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1461,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124665555</v>
+        <v>124667161</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>96445</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,43 +1528,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633142</v>
+        <v>632898</v>
       </c>
       <c r="R9" t="n">
-        <v>6898840</v>
+        <v>6898903</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1582,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124664023</v>
+        <v>124665985</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,43 +1640,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633092</v>
+        <v>633054</v>
       </c>
       <c r="R10" t="n">
-        <v>6898802</v>
+        <v>6898879</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1703,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124667024</v>
+        <v>124663369</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,38 +1748,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632896</v>
+        <v>632999</v>
       </c>
       <c r="R11" t="n">
-        <v>6898908</v>
+        <v>6898916</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,26 +1841,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1872,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124663547</v>
+        <v>124664880</v>
       </c>
       <c r="B12" t="n">
-        <v>74840</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1884,41 +1869,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633000</v>
+        <v>633177</v>
       </c>
       <c r="R12" t="n">
-        <v>6898916</v>
+        <v>6898718</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1947,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1957,12 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124664924</v>
+        <v>124663875</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2001,38 +1981,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633183</v>
+        <v>633040</v>
       </c>
       <c r="R13" t="n">
-        <v>6898714</v>
+        <v>6898800</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2064,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2074,7 +2054,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124664744</v>
+        <v>124676227</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79764</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,46 +2097,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633172</v>
+        <v>633194</v>
       </c>
       <c r="R14" t="n">
-        <v>6898735</v>
+        <v>6898707</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2183,19 +2157,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,6 +2173,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2222,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124667201</v>
+        <v>124665555</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2257,7 +2227,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2271,10 +2241,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632898</v>
+        <v>633142</v>
       </c>
       <c r="R15" t="n">
-        <v>6898903</v>
+        <v>6898840</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2306,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2316,7 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2455,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664880</v>
+        <v>124664616</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>74840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,25 +2437,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2495,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633177</v>
+        <v>633153</v>
       </c>
       <c r="R17" t="n">
-        <v>6898718</v>
+        <v>6898758</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2530,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2540,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2567,10 +2537,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124665985</v>
+        <v>124667024</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>96354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2579,25 +2549,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2607,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633054</v>
+        <v>632896</v>
       </c>
       <c r="R18" t="n">
-        <v>6898879</v>
+        <v>6898908</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2642,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,6 +2633,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2679,10 +2669,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124664466</v>
+        <v>124666936</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2691,38 +2681,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633170</v>
+        <v>632907</v>
       </c>
       <c r="R19" t="n">
-        <v>6898718</v>
+        <v>6898900</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2754,7 +2753,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2763,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,10 +2790,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124663875</v>
+        <v>124663547</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,25 +2802,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2831,13 +2830,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633040</v>
+        <v>633000</v>
       </c>
       <c r="R20" t="n">
-        <v>6898800</v>
+        <v>6898916</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2866,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2875,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,10 +2907,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124666936</v>
+        <v>124665963</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>4772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2915,35 +2919,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632907</v>
+        <v>633052</v>
       </c>
       <c r="R21" t="n">
-        <v>6898900</v>
+        <v>6898874</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664744</v>
+        <v>124664466</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,47 +937,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633172</v>
+        <v>633170</v>
       </c>
       <c r="R4" t="n">
-        <v>6898735</v>
+        <v>6898718</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664466</v>
+        <v>124664023</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,38 +1049,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633170</v>
+        <v>633092</v>
       </c>
       <c r="R5" t="n">
-        <v>6898718</v>
+        <v>6898802</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124664924</v>
+        <v>124664744</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,38 +1170,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633183</v>
+        <v>633172</v>
       </c>
       <c r="R6" t="n">
-        <v>6898714</v>
+        <v>6898735</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1270,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124667201</v>
+        <v>124664924</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,47 +1291,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632898</v>
+        <v>633183</v>
       </c>
       <c r="R7" t="n">
-        <v>6898903</v>
+        <v>6898714</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124664023</v>
+        <v>124667024</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>96354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,47 +1403,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633092</v>
+        <v>632896</v>
       </c>
       <c r="R8" t="n">
-        <v>6898802</v>
+        <v>6898908</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,6 +1487,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1512,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124667161</v>
+        <v>124665963</v>
       </c>
       <c r="B9" t="n">
-        <v>96445</v>
+        <v>4772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,38 +1535,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>990</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632898</v>
+        <v>633052</v>
       </c>
       <c r="R9" t="n">
-        <v>6898903</v>
+        <v>6898874</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,7 +1603,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1613,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124665985</v>
+        <v>124663875</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,25 +1652,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1664,10 +1680,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633054</v>
+        <v>633040</v>
       </c>
       <c r="R10" t="n">
-        <v>6898879</v>
+        <v>6898800</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1699,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124663369</v>
+        <v>124664880</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,47 +1764,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632999</v>
+        <v>633177</v>
       </c>
       <c r="R11" t="n">
-        <v>6898916</v>
+        <v>6898718</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1837,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664880</v>
+        <v>124663547</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>74840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,41 +1876,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633177</v>
+        <v>633000</v>
       </c>
       <c r="R12" t="n">
-        <v>6898718</v>
+        <v>6898916</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1932,7 +1939,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,7 +1949,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124663875</v>
+        <v>124664327</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,38 +1993,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633040</v>
+        <v>633161</v>
       </c>
       <c r="R13" t="n">
-        <v>6898800</v>
+        <v>6898722</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2044,7 +2056,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,7 +2066,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124676227</v>
+        <v>124666936</v>
       </c>
       <c r="B14" t="n">
-        <v>79764</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,40 +2109,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633194</v>
+        <v>632907</v>
       </c>
       <c r="R14" t="n">
-        <v>6898707</v>
+        <v>6898900</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,14 +2175,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2196,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2313,10 +2335,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124664327</v>
+        <v>124664616</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>74840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,25 +2347,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2353,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633161</v>
+        <v>633153</v>
       </c>
       <c r="R16" t="n">
-        <v>6898722</v>
+        <v>6898758</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2388,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,7 +2420,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664616</v>
+        <v>124663369</v>
       </c>
       <c r="B17" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,38 +2459,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633153</v>
+        <v>632999</v>
       </c>
       <c r="R17" t="n">
-        <v>6898758</v>
+        <v>6898916</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2500,7 +2531,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2541,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2568,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124667024</v>
+        <v>124665985</v>
       </c>
       <c r="B18" t="n">
-        <v>96354</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2549,25 +2580,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2608,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632896</v>
+        <v>633054</v>
       </c>
       <c r="R18" t="n">
-        <v>6898908</v>
+        <v>6898879</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2612,7 +2643,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2653,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,26 +2664,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2669,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124666936</v>
+        <v>124667161</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>96445</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2685,43 +2696,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>990</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632907</v>
+        <v>632898</v>
       </c>
       <c r="R19" t="n">
-        <v>6898900</v>
+        <v>6898903</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2753,7 +2755,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2763,7 +2765,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,10 +2792,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124663547</v>
+        <v>124676227</v>
       </c>
       <c r="B20" t="n">
-        <v>74840</v>
+        <v>79764</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2802,38 +2804,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>392</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633000</v>
+        <v>633194</v>
       </c>
       <c r="R20" t="n">
-        <v>6898916</v>
+        <v>6898707</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,24 +2868,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,6 +2884,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2907,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124665963</v>
+        <v>124667201</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2919,31 +2915,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633052</v>
+        <v>632898</v>
       </c>
       <c r="R21" t="n">
-        <v>6898874</v>
+        <v>6898903</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>124664466</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664023</v>
+        <v>124664880</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,47 +1049,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633092</v>
+        <v>633177</v>
       </c>
       <c r="R5" t="n">
-        <v>6898802</v>
+        <v>6898718</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124664744</v>
+        <v>124664327</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,47 +1161,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633172</v>
+        <v>633161</v>
       </c>
       <c r="R6" t="n">
-        <v>6898735</v>
+        <v>6898722</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124664924</v>
+        <v>124665985</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,38 +1273,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633183</v>
+        <v>633054</v>
       </c>
       <c r="R7" t="n">
-        <v>6898714</v>
+        <v>6898879</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124667024</v>
+        <v>124667201</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,38 +1385,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632896</v>
+        <v>632898</v>
       </c>
       <c r="R8" t="n">
-        <v>6898908</v>
+        <v>6898903</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,26 +1478,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1523,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124665963</v>
+        <v>124663369</v>
       </c>
       <c r="B9" t="n">
-        <v>4772</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,31 +1506,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1568,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633052</v>
+        <v>632999</v>
       </c>
       <c r="R9" t="n">
-        <v>6898874</v>
+        <v>6898916</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124663875</v>
+        <v>124676227</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,37 +1631,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633040</v>
+        <v>633194</v>
       </c>
       <c r="R10" t="n">
-        <v>6898800</v>
+        <v>6898707</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,19 +1691,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:44</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,6 +1707,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1752,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124664880</v>
+        <v>124664616</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>74964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,25 +1738,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1792,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633177</v>
+        <v>633153</v>
       </c>
       <c r="R11" t="n">
-        <v>6898718</v>
+        <v>6898758</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1827,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1837,7 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1864,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124663547</v>
+        <v>124664924</v>
       </c>
       <c r="B12" t="n">
-        <v>74840</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1876,41 +1850,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633000</v>
+        <v>633183</v>
       </c>
       <c r="R12" t="n">
-        <v>6898916</v>
+        <v>6898714</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1939,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1949,12 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124664327</v>
+        <v>124663875</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1993,38 +1962,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633161</v>
+        <v>633040</v>
       </c>
       <c r="R13" t="n">
-        <v>6898722</v>
+        <v>6898800</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2056,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2066,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,10 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124666936</v>
+        <v>124665555</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,7 +2097,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2142,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632907</v>
+        <v>633142</v>
       </c>
       <c r="R14" t="n">
-        <v>6898900</v>
+        <v>6898840</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2177,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2187,7 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2214,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124665555</v>
+        <v>124664023</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>100451</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,35 +2195,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2263,10 +2232,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633142</v>
+        <v>633092</v>
       </c>
       <c r="R15" t="n">
-        <v>6898840</v>
+        <v>6898802</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2298,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2308,7 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2335,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124664616</v>
+        <v>124667024</v>
       </c>
       <c r="B16" t="n">
-        <v>74840</v>
+        <v>96522</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,38 +2316,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633153</v>
+        <v>632896</v>
       </c>
       <c r="R16" t="n">
-        <v>6898758</v>
+        <v>6898908</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2410,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,6 +2400,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2447,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124663369</v>
+        <v>124664744</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2492,14 +2481,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632999</v>
+        <v>633172</v>
       </c>
       <c r="R17" t="n">
-        <v>6898916</v>
+        <v>6898735</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2531,7 +2520,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2541,7 +2530,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2568,10 +2557,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124665985</v>
+        <v>124665963</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>4772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2584,34 +2573,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633054</v>
+        <v>633052</v>
       </c>
       <c r="R18" t="n">
-        <v>6898879</v>
+        <v>6898874</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2680,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124667161</v>
+        <v>124663547</v>
       </c>
       <c r="B19" t="n">
-        <v>96445</v>
+        <v>74964</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,25 +2686,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>990</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2720,13 +2714,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>632898</v>
+        <v>633000</v>
       </c>
       <c r="R19" t="n">
-        <v>6898903</v>
+        <v>6898916</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2755,7 +2749,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2765,7 +2759,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2792,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124676227</v>
+        <v>124667161</v>
       </c>
       <c r="B20" t="n">
-        <v>79764</v>
+        <v>96613</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2808,40 +2807,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>392</v>
+        <v>990</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633194</v>
+        <v>632898</v>
       </c>
       <c r="R20" t="n">
-        <v>6898707</v>
+        <v>6898903</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2868,14 +2864,19 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,7 +2885,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124667201</v>
+        <v>124666936</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632898</v>
+        <v>632907</v>
       </c>
       <c r="R21" t="n">
-        <v>6898903</v>
+        <v>6898900</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3022,6 +3022,117 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124664436</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80005</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>392</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>633158</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6898732</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3133,6 +3133,1125 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128305231</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Björkön, Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>632937</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6898992</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128305026</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90897</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Björkön, Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>632891</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6898892</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128304085</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92152</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>633181</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6898798</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128304130</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>633184</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6898814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128305266</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Björkön, Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>632888</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6898987</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128304580</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92287</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Björkön, Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>632990</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6898901</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128304014</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>633120</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6898768</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128304896</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96722</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>53</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Björkön, Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>632946</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6898836</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128304456</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Björkön, Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>633003</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6898913</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128305217</v>
+      </c>
+      <c r="B32" t="n">
+        <v>75145</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>308</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Björkön, Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>632940</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6898980</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128304493</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Björkön, Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>632983</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6898891</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,31 +3468,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R26" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3525,6 +3516,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3562,16 +3558,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3579,22 +3575,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R27" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3627,11 +3632,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3237,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305026</v>
+        <v>128304085</v>
       </c>
       <c r="B24" t="n">
-        <v>90897</v>
+        <v>92152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,43 +3248,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5754</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>632891</v>
+        <v>633181</v>
       </c>
       <c r="R24" t="n">
-        <v>6898892</v>
+        <v>6898798</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3343,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128304085</v>
+        <v>128305026</v>
       </c>
       <c r="B25" t="n">
-        <v>92152</v>
+        <v>90897</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3354,34 +3345,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2014</v>
+        <v>5754</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633181</v>
+        <v>632891</v>
       </c>
       <c r="R25" t="n">
-        <v>6898798</v>
+        <v>6898892</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3237,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128304085</v>
+        <v>128305026</v>
       </c>
       <c r="B24" t="n">
-        <v>92152</v>
+        <v>90897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,34 +3248,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>5754</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633181</v>
+        <v>632891</v>
       </c>
       <c r="R24" t="n">
-        <v>6898798</v>
+        <v>6898892</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3334,10 +3343,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305026</v>
+        <v>128304085</v>
       </c>
       <c r="B25" t="n">
-        <v>90897</v>
+        <v>92152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,43 +3354,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5754</v>
+        <v>2014</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>632891</v>
+        <v>633181</v>
       </c>
       <c r="R25" t="n">
-        <v>6898892</v>
+        <v>6898798</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,22 +3468,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R26" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3516,11 +3525,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3551,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3558,16 +3562,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3575,31 +3579,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R27" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3632,6 +3627,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3237,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305026</v>
+        <v>128304085</v>
       </c>
       <c r="B24" t="n">
-        <v>90897</v>
+        <v>92152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,43 +3248,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5754</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>632891</v>
+        <v>633181</v>
       </c>
       <c r="R24" t="n">
-        <v>6898892</v>
+        <v>6898798</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3343,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128304085</v>
+        <v>128305026</v>
       </c>
       <c r="B25" t="n">
-        <v>92152</v>
+        <v>90897</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3354,34 +3345,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2014</v>
+        <v>5754</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633181</v>
+        <v>632891</v>
       </c>
       <c r="R25" t="n">
-        <v>6898798</v>
+        <v>6898892</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,31 +3468,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R26" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3525,6 +3516,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3562,16 +3558,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3579,22 +3575,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R27" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3627,11 +3632,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3027,7 +3027,7 @@
         <v>124664436</v>
       </c>
       <c r="B22" t="n">
-        <v>80005</v>
+        <v>80008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>128305231</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128304085</v>
       </c>
       <c r="B24" t="n">
-        <v>92152</v>
+        <v>92160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>128305026</v>
       </c>
       <c r="B25" t="n">
-        <v>90897</v>
+        <v>90903</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>57686</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,22 +3468,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R26" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3516,11 +3525,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3551,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>57673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3558,16 +3562,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3575,31 +3579,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R27" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3632,6 +3627,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,7 +3661,7 @@
         <v>128304580</v>
       </c>
       <c r="B28" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>128304014</v>
       </c>
       <c r="B29" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>128304896</v>
       </c>
       <c r="B30" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128304456</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>128305217</v>
       </c>
       <c r="B32" t="n">
-        <v>75145</v>
+        <v>75148</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128304493</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B26" t="n">
-        <v>57686</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,31 +3468,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R26" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3525,6 +3516,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>57686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3562,16 +3558,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3579,22 +3575,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R27" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3627,11 +3632,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3027,7 +3027,7 @@
         <v>124664436</v>
       </c>
       <c r="B22" t="n">
-        <v>80008</v>
+        <v>80061</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>128305231</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128304085</v>
       </c>
       <c r="B24" t="n">
-        <v>92160</v>
+        <v>92252</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>128305026</v>
       </c>
       <c r="B25" t="n">
-        <v>90903</v>
+        <v>90995</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>128305266</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>128304130</v>
       </c>
       <c r="B27" t="n">
-        <v>57686</v>
+        <v>57698</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128304580</v>
       </c>
       <c r="B28" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>128304014</v>
       </c>
       <c r="B29" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>128304896</v>
       </c>
       <c r="B30" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128304456</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>128305217</v>
       </c>
       <c r="B32" t="n">
-        <v>75148</v>
+        <v>75163</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128304493</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305217</v>
+        <v>128304493</v>
       </c>
       <c r="B32" t="n">
-        <v>75163</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,34 +4066,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>632940</v>
+        <v>632983</v>
       </c>
       <c r="R32" t="n">
-        <v>6898980</v>
+        <v>6898891</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4152,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128304493</v>
+        <v>128305217</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>75163</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,39 +4168,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>632983</v>
+        <v>632940</v>
       </c>
       <c r="R33" t="n">
-        <v>6898891</v>
+        <v>6898980</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128304493</v>
+        <v>128305217</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>75163</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,39 +4066,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>632983</v>
+        <v>632940</v>
       </c>
       <c r="R32" t="n">
-        <v>6898891</v>
+        <v>6898980</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4157,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305217</v>
+        <v>128304493</v>
       </c>
       <c r="B33" t="n">
-        <v>75163</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,34 +4163,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>632940</v>
+        <v>632983</v>
       </c>
       <c r="R33" t="n">
-        <v>6898980</v>
+        <v>6898891</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3027,7 +3027,7 @@
         <v>124664436</v>
       </c>
       <c r="B22" t="n">
-        <v>80061</v>
+        <v>80065</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>128305231</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128304085</v>
       </c>
       <c r="B24" t="n">
-        <v>92252</v>
+        <v>92264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>128305026</v>
       </c>
       <c r="B25" t="n">
-        <v>90995</v>
+        <v>91007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57702</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,22 +3468,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R26" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3516,11 +3525,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3551,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B27" t="n">
-        <v>57698</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3558,16 +3562,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3575,31 +3579,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R27" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3632,6 +3627,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,7 +3661,7 @@
         <v>128304580</v>
       </c>
       <c r="B28" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>128304014</v>
       </c>
       <c r="B29" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>128304896</v>
       </c>
       <c r="B30" t="n">
-        <v>96823</v>
+        <v>96835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128304456</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>128304493</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>128305217</v>
       </c>
       <c r="B33" t="n">
-        <v>75163</v>
+        <v>75167</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3027,7 +3027,7 @@
         <v>124664436</v>
       </c>
       <c r="B22" t="n">
-        <v>80065</v>
+        <v>80067</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128304085</v>
       </c>
       <c r="B24" t="n">
-        <v>92264</v>
+        <v>92266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>128305026</v>
       </c>
       <c r="B25" t="n">
-        <v>91007</v>
+        <v>91009</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B26" t="n">
-        <v>57702</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,31 +3468,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R26" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3525,6 +3516,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>57702</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3562,16 +3558,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3579,22 +3575,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R27" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3627,11 +3632,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,7 +3661,7 @@
         <v>128304580</v>
       </c>
       <c r="B28" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>128304014</v>
       </c>
       <c r="B29" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>128304896</v>
       </c>
       <c r="B30" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128304456</v>
       </c>
       <c r="B31" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128304493</v>
+        <v>128305217</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>75169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,39 +4066,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>632983</v>
+        <v>632940</v>
       </c>
       <c r="R32" t="n">
-        <v>6898891</v>
+        <v>6898980</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4157,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305217</v>
+        <v>128304493</v>
       </c>
       <c r="B33" t="n">
-        <v>75167</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,34 +4163,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>632940</v>
+        <v>632983</v>
       </c>
       <c r="R33" t="n">
-        <v>6898980</v>
+        <v>6898891</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3237,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128304085</v>
+        <v>128305026</v>
       </c>
       <c r="B24" t="n">
-        <v>92266</v>
+        <v>91009</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,34 +3248,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>5754</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633181</v>
+        <v>632891</v>
       </c>
       <c r="R24" t="n">
-        <v>6898798</v>
+        <v>6898892</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3334,10 +3343,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305026</v>
+        <v>128304085</v>
       </c>
       <c r="B25" t="n">
-        <v>91009</v>
+        <v>92266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,43 +3354,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5754</v>
+        <v>2014</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>632891</v>
+        <v>633181</v>
       </c>
       <c r="R25" t="n">
-        <v>6898892</v>
+        <v>6898798</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57702</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,22 +3468,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R26" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3516,11 +3525,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3551,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B27" t="n">
-        <v>57702</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3558,16 +3562,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3575,31 +3579,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R27" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3632,6 +3627,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3961,7 +3961,7 @@
         <v>128304456</v>
       </c>
       <c r="B31" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305217</v>
+        <v>128304493</v>
       </c>
       <c r="B32" t="n">
-        <v>75169</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,34 +4066,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>632940</v>
+        <v>632983</v>
       </c>
       <c r="R32" t="n">
-        <v>6898980</v>
+        <v>6898891</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4152,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128304493</v>
+        <v>128305217</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>75169</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,39 +4168,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>632983</v>
+        <v>632940</v>
       </c>
       <c r="R33" t="n">
-        <v>6898891</v>
+        <v>6898980</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3237,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305026</v>
+        <v>128304085</v>
       </c>
       <c r="B24" t="n">
-        <v>91009</v>
+        <v>92267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,43 +3248,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5754</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>632891</v>
+        <v>633181</v>
       </c>
       <c r="R24" t="n">
-        <v>6898892</v>
+        <v>6898798</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3343,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128304085</v>
+        <v>128305026</v>
       </c>
       <c r="B25" t="n">
-        <v>92266</v>
+        <v>91010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3354,34 +3345,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2014</v>
+        <v>5754</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633181</v>
+        <v>632891</v>
       </c>
       <c r="R25" t="n">
-        <v>6898798</v>
+        <v>6898892</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3661,7 +3661,7 @@
         <v>128304580</v>
       </c>
       <c r="B28" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>128304014</v>
       </c>
       <c r="B29" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>128304896</v>
       </c>
       <c r="B30" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128304456</v>
       </c>
       <c r="B31" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128304493</v>
+        <v>128305217</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>75169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,39 +4066,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>632983</v>
+        <v>632940</v>
       </c>
       <c r="R32" t="n">
-        <v>6898891</v>
+        <v>6898980</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4157,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305217</v>
+        <v>128304493</v>
       </c>
       <c r="B33" t="n">
-        <v>75169</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,34 +4163,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>632940</v>
+        <v>632983</v>
       </c>
       <c r="R33" t="n">
-        <v>6898980</v>
+        <v>6898891</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3237,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128304085</v>
+        <v>128305026</v>
       </c>
       <c r="B24" t="n">
-        <v>92267</v>
+        <v>91010</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,34 +3248,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>5754</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633181</v>
+        <v>632891</v>
       </c>
       <c r="R24" t="n">
-        <v>6898798</v>
+        <v>6898892</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3334,10 +3343,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305026</v>
+        <v>128304085</v>
       </c>
       <c r="B25" t="n">
-        <v>91010</v>
+        <v>92267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,43 +3354,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5754</v>
+        <v>2014</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>632891</v>
+        <v>633181</v>
       </c>
       <c r="R25" t="n">
-        <v>6898892</v>
+        <v>6898798</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3027,7 +3027,7 @@
         <v>124664436</v>
       </c>
       <c r="B22" t="n">
-        <v>80067</v>
+        <v>80094</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>128305231</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128305026</v>
       </c>
       <c r="B24" t="n">
-        <v>91010</v>
+        <v>91037</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>128304085</v>
       </c>
       <c r="B25" t="n">
-        <v>92267</v>
+        <v>92294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>128304130</v>
       </c>
       <c r="B26" t="n">
-        <v>57702</v>
+        <v>57729</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>128305266</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128304580</v>
       </c>
       <c r="B28" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>128304014</v>
       </c>
       <c r="B29" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>128304896</v>
       </c>
       <c r="B30" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128304456</v>
       </c>
       <c r="B31" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>128305217</v>
       </c>
       <c r="B32" t="n">
-        <v>75169</v>
+        <v>75196</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128304493</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3237,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305026</v>
+        <v>128304085</v>
       </c>
       <c r="B24" t="n">
-        <v>91037</v>
+        <v>92294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,43 +3248,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5754</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>632891</v>
+        <v>633181</v>
       </c>
       <c r="R24" t="n">
-        <v>6898892</v>
+        <v>6898798</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3343,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128304085</v>
+        <v>128305026</v>
       </c>
       <c r="B25" t="n">
-        <v>92294</v>
+        <v>91037</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3354,34 +3345,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2014</v>
+        <v>5754</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633181</v>
+        <v>632891</v>
       </c>
       <c r="R25" t="n">
-        <v>6898798</v>
+        <v>6898892</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128304130</v>
+        <v>128305266</v>
       </c>
       <c r="B26" t="n">
-        <v>57729</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3468,31 +3468,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633184</v>
+        <v>632888</v>
       </c>
       <c r="R26" t="n">
-        <v>6898814</v>
+        <v>6898987</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3525,6 +3516,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305266</v>
+        <v>128304130</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>57729</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3562,16 +3558,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3579,22 +3575,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632888</v>
+        <v>633184</v>
       </c>
       <c r="R27" t="n">
-        <v>6898987</v>
+        <v>6898814</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3627,11 +3632,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305217</v>
+        <v>128304493</v>
       </c>
       <c r="B32" t="n">
-        <v>75196</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,34 +4066,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>632940</v>
+        <v>632983</v>
       </c>
       <c r="R32" t="n">
-        <v>6898980</v>
+        <v>6898891</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4152,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128304493</v>
+        <v>128305217</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>75196</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,39 +4168,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>632983</v>
+        <v>632940</v>
       </c>
       <c r="R33" t="n">
-        <v>6898891</v>
+        <v>6898980</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3138,7 +3138,7 @@
         <v>128305231</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>128305266</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128304493</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -3138,7 +3138,7 @@
         <v>128305231</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>128305266</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128304493</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>124676227</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>124676227</v>
       </c>
       <c r="B10" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>124676227</v>
       </c>
       <c r="B10" t="n">
-        <v>80223</v>
+        <v>80224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>124676227</v>
       </c>
       <c r="B10" t="n">
-        <v>80224</v>
+        <v>80226</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>124676227</v>
       </c>
       <c r="B10" t="n">
-        <v>80226</v>
+        <v>80227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>124676227</v>
       </c>
       <c r="B10" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>124676227</v>
       </c>
       <c r="B10" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17278360</v>
+        <v>124667024</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jungfrutjärnarna, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633021.8387308395</v>
+        <v>632896</v>
       </c>
       <c r="R2" t="n">
-        <v>6898855.827302166</v>
+        <v>6898908</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-11-15</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-11-15</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,81 +767,83 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Löv/barrblandskog</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead wood # Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17278483</v>
+        <v>128304896</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jungfrutjärnarna, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633021.8387308395</v>
+        <v>632946</v>
       </c>
       <c r="R3" t="n">
-        <v>6898855.827302166</v>
+        <v>6898836</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-11-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,40 +883,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Löv/barrblandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664466</v>
+        <v>128305217</v>
       </c>
       <c r="B4" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,34 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633170</v>
+        <v>632940</v>
       </c>
       <c r="R4" t="n">
-        <v>6898718</v>
+        <v>6898980</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,50 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664880</v>
+        <v>124664436</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633177</v>
+        <v>633158</v>
       </c>
       <c r="R5" t="n">
-        <v>6898718</v>
+        <v>6898732</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1069,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1079,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,6 +1088,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1149,53 +1107,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124664327</v>
+        <v>124676227</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633161</v>
+        <v>633194</v>
       </c>
       <c r="R6" t="n">
-        <v>6898722</v>
+        <v>6898707</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,19 +1178,14 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:57</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,6 +1194,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1261,37 +1213,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124665985</v>
+        <v>124667161</v>
       </c>
       <c r="B7" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633054</v>
+        <v>632898</v>
       </c>
       <c r="R7" t="n">
-        <v>6898879</v>
+        <v>6898903</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,59 +1320,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124667201</v>
+        <v>128304085</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2014</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632898</v>
+        <v>633181</v>
       </c>
       <c r="R8" t="n">
-        <v>6898903</v>
+        <v>6898798</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,22 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,59 +1417,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124663369</v>
+        <v>128304014</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632999</v>
+        <v>633120</v>
       </c>
       <c r="R9" t="n">
-        <v>6898916</v>
+        <v>6898768</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,22 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,51 +1523,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124676227</v>
+        <v>128304580</v>
       </c>
       <c r="B10" t="n">
-        <v>80231</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633194</v>
+        <v>632990</v>
       </c>
       <c r="R10" t="n">
-        <v>6898707</v>
+        <v>6898901</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,17 +1588,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera bålar, från ca 5cm breda upp till ca 15-18cm. På asp.</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1602,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1721,15 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124664616</v>
+        <v>124665985</v>
       </c>
       <c r="B11" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,34 +1631,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633153</v>
+        <v>633054</v>
       </c>
       <c r="R11" t="n">
-        <v>6898758</v>
+        <v>6898879</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1796,7 +1690,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1700,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,15 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124664924</v>
+        <v>128305026</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,34 +1738,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5754</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633183</v>
+        <v>632891</v>
       </c>
       <c r="R12" t="n">
-        <v>6898714</v>
+        <v>6898892</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1903,22 +1801,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,15 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124663875</v>
+        <v>124664880</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,34 +1844,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633040</v>
+        <v>633177</v>
       </c>
       <c r="R13" t="n">
-        <v>6898800</v>
+        <v>6898718</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2020,7 +1903,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +1913,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,62 +1940,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124665555</v>
+        <v>124663547</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633142</v>
+        <v>633000</v>
       </c>
       <c r="R14" t="n">
-        <v>6898840</v>
+        <v>6898916</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2141,7 +2010,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2020,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Förekommer på många träd i beståndet</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,59 +2052,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124664023</v>
+        <v>124664616</v>
       </c>
       <c r="B15" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633092</v>
+        <v>633153</v>
       </c>
       <c r="R15" t="n">
-        <v>6898802</v>
+        <v>6898758</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2262,7 +2122,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2132,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,15 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124667024</v>
+        <v>124664327</v>
       </c>
       <c r="B16" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,34 +2170,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632896</v>
+        <v>633161</v>
       </c>
       <c r="R16" t="n">
-        <v>6898908</v>
+        <v>6898722</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2374,7 +2229,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2239,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,26 +2250,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2431,59 +2266,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124664744</v>
+        <v>124664466</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633172</v>
+        <v>633170</v>
       </c>
       <c r="R17" t="n">
-        <v>6898735</v>
+        <v>6898718</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2515,7 +2336,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,7 +2346,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,55 +2373,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124665963</v>
+        <v>124664924</v>
       </c>
       <c r="B18" t="n">
-        <v>4772</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633052</v>
+        <v>633183</v>
       </c>
       <c r="R18" t="n">
-        <v>6898874</v>
+        <v>6898714</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2632,7 +2443,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2642,7 +2453,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,53 +2480,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124663547</v>
+        <v>128304130</v>
       </c>
       <c r="B19" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björkön, Björkön, Mpd</t>
+          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633000</v>
+        <v>633184</v>
       </c>
       <c r="R19" t="n">
-        <v>6898916</v>
+        <v>6898814</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2739,27 +2559,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Förekommer på många träd i beståndet</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,50 +2591,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124667161</v>
+        <v>128304493</v>
       </c>
       <c r="B20" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>990</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>632898</v>
+        <v>632983</v>
       </c>
       <c r="R20" t="n">
-        <v>6898903</v>
+        <v>6898891</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2856,22 +2661,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:17</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:17</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,47 +2693,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124666936</v>
+        <v>128305231</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2947,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>632907</v>
+        <v>632937</v>
       </c>
       <c r="R21" t="n">
-        <v>6898900</v>
+        <v>6898992</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2977,22 +2763,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,48 +2795,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124664436</v>
+        <v>128305266</v>
       </c>
       <c r="B22" t="n">
-        <v>80094</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>392</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633158</v>
+        <v>632888</v>
       </c>
       <c r="R22" t="n">
-        <v>6898732</v>
+        <v>6898987</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3087,22 +2865,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,7 +2884,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3130,38 +2902,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128305231</v>
+        <v>124665963</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>4775</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3170,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>632937</v>
+        <v>633052</v>
       </c>
       <c r="R23" t="n">
-        <v>6898992</v>
+        <v>6898874</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3200,12 +2972,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,42 +3014,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305026</v>
+        <v>124663369</v>
       </c>
       <c r="B24" t="n">
-        <v>91047</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3276,10 +3058,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>632891</v>
+        <v>632999</v>
       </c>
       <c r="R24" t="n">
-        <v>6898892</v>
+        <v>6898916</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3306,12 +3088,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3338,45 +3130,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128304085</v>
+        <v>124663875</v>
       </c>
       <c r="B25" t="n">
-        <v>92304</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2014</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633181</v>
+        <v>633040</v>
       </c>
       <c r="R25" t="n">
-        <v>6898798</v>
+        <v>6898800</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3403,12 +3195,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,59 +3237,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128304130</v>
+        <v>124664744</v>
       </c>
       <c r="B26" t="n">
-        <v>57729</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633184</v>
+        <v>633172</v>
       </c>
       <c r="R26" t="n">
-        <v>6898814</v>
+        <v>6898735</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3514,12 +3311,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,38 +3353,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305266</v>
+        <v>124665555</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3586,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>632888</v>
+        <v>633142</v>
       </c>
       <c r="R27" t="n">
-        <v>6898987</v>
+        <v>6898840</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3616,17 +3427,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack i en äldre gran. Äldre spår av tretåig finns på flera platser i närheten, likaså gammalt bohål.</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,45 +3469,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128304580</v>
+        <v>124666936</v>
       </c>
       <c r="B28" t="n">
-        <v>92439</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>632990</v>
+        <v>632907</v>
       </c>
       <c r="R28" t="n">
-        <v>6898901</v>
+        <v>6898900</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3718,12 +3543,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3750,54 +3585,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128304014</v>
+        <v>124667201</v>
       </c>
       <c r="B29" t="n">
-        <v>92786</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ännsikslandet, Ännsikslandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>633120</v>
+        <v>632898</v>
       </c>
       <c r="R29" t="n">
-        <v>6898768</v>
+        <v>6898903</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3824,12 +3659,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3856,32 +3701,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128304896</v>
+        <v>128304456</v>
       </c>
       <c r="B30" t="n">
-        <v>96878</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3891,10 +3736,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>632946</v>
+        <v>633003</v>
       </c>
       <c r="R30" t="n">
-        <v>6898836</v>
+        <v>6898913</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3953,45 +3798,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128304456</v>
+        <v>124664023</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633003</v>
+        <v>633092</v>
       </c>
       <c r="R31" t="n">
-        <v>6898913</v>
+        <v>6898802</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4018,12 +3872,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4047,205 +3911,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>128305217</v>
-      </c>
-      <c r="B32" t="n">
-        <v>75197</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>308</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Björkön, Björkön, Mpd</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>632940</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6898980</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Njurunda</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>128304493</v>
-      </c>
-      <c r="B33" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Björkön, Björkön, Mpd</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>632983</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6898891</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Njurunda</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13934-2025 artfynd.xlsx
+++ b/artfynd/A 13934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124667024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128304896</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305217</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664436</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676227</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124667161</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128304085</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128304014</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128304580</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124665985</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664880</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2049,6 +2114,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124663547</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664616</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2263,6 +2338,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664327</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664466</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2477,6 +2562,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664924</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128304130</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2690,6 +2785,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128304493</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305231</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2899,6 +3004,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305266</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3011,6 +3121,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124665963</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3127,6 +3242,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124663369</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3234,6 +3354,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124663875</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3350,6 +3475,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664744</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3466,6 +3596,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124665555</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3582,6 +3717,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124666936</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3698,6 +3838,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124667201</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3795,6 +3940,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128304456</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3911,8 +4061,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>